--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.13045771258134</v>
+        <v>1.993875654572231</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.27003448274445</v>
+        <v>2.022576910159237</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.921092557336677</v>
+        <v>1.950823771191723</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>350590.0389707951</v>
+        <v>299647.5576562535</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.60808974475826</v>
+        <v>8.282392258131448</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>440.89</v>
+        <v>432.5857149969322</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1194.824933333334</v>
+        <v>1093.332224339679</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1007.214933333333</v>
+        <v>897.4179393366113</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.27003448274445</v>
+        <v>2.022576910159237</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.27003448274445</v>
+        <v>2.022576910159237</v>
       </c>
     </row>
     <row r="14">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.638080293687021</v>
+        <v>1.677694488449005</v>
       </c>
       <c r="F13" t="n">
-        <v>1.229410715425761</v>
+        <v>1.259141929280808</v>
       </c>
     </row>
     <row r="14">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.921092557336677</v>
+        <v>1.950823771191723</v>
       </c>
     </row>
     <row r="15">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.463785293774217</v>
+        <v>1.351949851934291</v>
       </c>
       <c r="C2" t="n">
-        <v>1.785224079188511</v>
+        <v>1.659409207118594</v>
       </c>
       <c r="D2" t="n">
-        <v>2.106662864602804</v>
+        <v>1.966868562302899</v>
       </c>
       <c r="E2" t="n">
-        <v>2.428101650017099</v>
+        <v>2.274327917487202</v>
       </c>
       <c r="F2" t="n">
-        <v>2.749540435431392</v>
+        <v>2.581787272671505</v>
       </c>
     </row>
     <row r="3">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.47512336660504</v>
+        <v>1.363287924765114</v>
       </c>
       <c r="C3" t="n">
-        <v>1.796562152019334</v>
+        <v>1.670747279949418</v>
       </c>
       <c r="D3" t="n">
-        <v>2.118000937433627</v>
+        <v>1.978206635133722</v>
       </c>
       <c r="E3" t="n">
-        <v>2.439439722847923</v>
+        <v>2.285665990318025</v>
       </c>
       <c r="F3" t="n">
-        <v>2.760878508262216</v>
+        <v>2.593125345502329</v>
       </c>
     </row>
     <row r="4">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.486461439435863</v>
+        <v>1.374625997595938</v>
       </c>
       <c r="C4" t="n">
-        <v>1.807900224850157</v>
+        <v>1.682085352780241</v>
       </c>
       <c r="D4" t="n">
-        <v>2.129339010264451</v>
+        <v>1.989544707964545</v>
       </c>
       <c r="E4" t="n">
-        <v>2.450777795678746</v>
+        <v>2.297004063148849</v>
       </c>
       <c r="F4" t="n">
-        <v>2.772216581093039</v>
+        <v>2.604463418333152</v>
       </c>
     </row>
     <row r="5">
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.497799512266687</v>
+        <v>1.385964070426761</v>
       </c>
       <c r="C5" t="n">
-        <v>1.819238297680981</v>
+        <v>1.693423425611064</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140677083095274</v>
+        <v>2.000882780795369</v>
       </c>
       <c r="E5" t="n">
-        <v>2.462115868509569</v>
+        <v>2.308342135979672</v>
       </c>
       <c r="F5" t="n">
-        <v>2.783554653923862</v>
+        <v>2.615801491163975</v>
       </c>
     </row>
     <row r="6">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.50913758509751</v>
+        <v>1.397302143257584</v>
       </c>
       <c r="C6" t="n">
-        <v>1.830576370511804</v>
+        <v>1.704761498441888</v>
       </c>
       <c r="D6" t="n">
-        <v>2.152015155926097</v>
+        <v>2.012220853626192</v>
       </c>
       <c r="E6" t="n">
-        <v>2.473453941340392</v>
+        <v>2.319680208810495</v>
       </c>
       <c r="F6" t="n">
-        <v>2.794892726754686</v>
+        <v>2.627139563994799</v>
       </c>
     </row>
   </sheetData>
@@ -1272,7 +1272,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -1280,7 +1280,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.993875654572231</v>
+        <v>2.189469675646569</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.950823771191723</v>
+        <v>2.439808823877566</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299647.5576562535</v>
+        <v>137798.8835626314</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.282392258131448</v>
+        <v>3.808822655940233</v>
       </c>
     </row>
   </sheetData>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.677694488449005</v>
+        <v>2.329223524809156</v>
       </c>
       <c r="F13" t="n">
-        <v>1.259141929280808</v>
+        <v>1.748126981966651</v>
       </c>
     </row>
     <row r="14">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.950823771191723</v>
+        <v>2.439808823877566</v>
       </c>
     </row>
     <row r="15">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351949851934291</v>
+        <v>1.480633534631111</v>
       </c>
       <c r="C2" t="n">
-        <v>1.659409207118594</v>
+        <v>1.783037143015192</v>
       </c>
       <c r="D2" t="n">
-        <v>1.966868562302899</v>
+        <v>2.085440751399275</v>
       </c>
       <c r="E2" t="n">
-        <v>2.274327917487202</v>
+        <v>2.387844359783355</v>
       </c>
       <c r="F2" t="n">
-        <v>2.581787272671505</v>
+        <v>2.690247968167437</v>
       </c>
     </row>
     <row r="3">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363287924765114</v>
+        <v>1.502565917026686</v>
       </c>
       <c r="C3" t="n">
-        <v>1.670747279949418</v>
+        <v>1.804969525410768</v>
       </c>
       <c r="D3" t="n">
-        <v>1.978206635133722</v>
+        <v>2.10737313379485</v>
       </c>
       <c r="E3" t="n">
-        <v>2.285665990318025</v>
+        <v>2.409776742178931</v>
       </c>
       <c r="F3" t="n">
-        <v>2.593125345502329</v>
+        <v>2.712180350563012</v>
       </c>
     </row>
     <row r="4">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.374625997595938</v>
+        <v>1.524498299422262</v>
       </c>
       <c r="C4" t="n">
-        <v>1.682085352780241</v>
+        <v>1.826901907806343</v>
       </c>
       <c r="D4" t="n">
-        <v>1.989544707964545</v>
+        <v>2.129305516190425</v>
       </c>
       <c r="E4" t="n">
-        <v>2.297004063148849</v>
+        <v>2.431709124574506</v>
       </c>
       <c r="F4" t="n">
-        <v>2.604463418333152</v>
+        <v>2.734112732958587</v>
       </c>
     </row>
     <row r="5">
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.385964070426761</v>
+        <v>1.546430681817837</v>
       </c>
       <c r="C5" t="n">
-        <v>1.693423425611064</v>
+        <v>1.848834290201918</v>
       </c>
       <c r="D5" t="n">
-        <v>2.000882780795369</v>
+        <v>2.151237898586</v>
       </c>
       <c r="E5" t="n">
-        <v>2.308342135979672</v>
+        <v>2.453641506970081</v>
       </c>
       <c r="F5" t="n">
-        <v>2.615801491163975</v>
+        <v>2.756045115354162</v>
       </c>
     </row>
     <row r="6">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.397302143257584</v>
+        <v>1.568363064213412</v>
       </c>
       <c r="C6" t="n">
-        <v>1.704761498441888</v>
+        <v>1.870766672597493</v>
       </c>
       <c r="D6" t="n">
-        <v>2.012220853626192</v>
+        <v>2.173170280981575</v>
       </c>
       <c r="E6" t="n">
-        <v>2.319680208810495</v>
+        <v>2.475573889365656</v>
       </c>
       <c r="F6" t="n">
-        <v>2.627139563994799</v>
+        <v>2.777977497749737</v>
       </c>
     </row>
   </sheetData>
@@ -1272,7 +1272,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="3">
@@ -1280,7 +1280,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="4">
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137798.8835626314</v>
+        <v>155119.30428119</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.808822655940233</v>
+        <v>4.287566816543524</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>155119.30428119</v>
+        <v>157593.6500981269</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.287566816543524</v>
+        <v>4.355958839486851</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1294,35 +1293,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>157593.6500981269</v>
+        <v>140273.2293795683</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.355958839486851</v>
+        <v>3.87721467888356</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>140273.2293795683</v>
+        <v>108106.7337593882</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.87721467888356</v>
+        <v>2.988118380620308</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108106.7337593882</v>
+        <v>113055.4253932621</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.988118380620308</v>
+        <v>3.124902426506964</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.189469675646569</v>
+        <v>2.209783772116895</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.022576910159237</v>
+        <v>2.041106685901538</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.439808823877566</v>
+        <v>2.462799401439929</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43400</v>
+        <v>46350</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42481.25</v>
+        <v>44825</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.20572655796614</v>
+        <v>1.310820323135168</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>113055.4253932621</v>
+        <v>132543.4122991888</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.124902426506964</v>
+        <v>3.437865933277382</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>432.5857149969322</v>
+        <v>440.8073816635988</v>
       </c>
     </row>
     <row r="3">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>897.4179393366113</v>
+        <v>905.639606003278</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.022576910159237</v>
+        <v>2.041106685901538</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.022576910159237</v>
+        <v>2.041106685901538</v>
       </c>
     </row>
     <row r="14">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43375</v>
+        <v>46350</v>
       </c>
       <c r="C2" t="n">
         <v>26404.2380952381</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42875</v>
+        <v>45325</v>
       </c>
       <c r="C3" t="n">
         <v>26404.2380952381</v>
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42350</v>
+        <v>44325</v>
       </c>
       <c r="C4" t="n">
-        <v>26946.394</v>
+        <v>27013.544</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1343667910479272</v>
+        <v>0.1352631264630104</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0671833955239636</v>
+        <v>0.0676315632315052</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06212547405718579</v>
+        <v>0.06253990132855246</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41325</v>
+        <v>43300</v>
       </c>
       <c r="C5" t="n">
-        <v>28463.30323809524</v>
+        <v>28735.85323809524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1429837657115454</v>
+        <v>0.1459371771488864</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0714918828557727</v>
+        <v>0.0729685885744432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06440710167186729</v>
+        <v>0.06573746718418307</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40800</v>
+        <v>42275</v>
       </c>
       <c r="C6" t="n">
-        <v>28808.33033333334</v>
+        <v>29054.65533333334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1516328504046028</v>
+        <v>0.1548850100820818</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07581642520230139</v>
+        <v>0.07744250504104089</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06654410369835957</v>
+        <v>0.06797131455830406</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39775</v>
+        <v>41275</v>
       </c>
       <c r="C7" t="n">
-        <v>29426.03028571429</v>
+        <v>29765.03028571429</v>
       </c>
       <c r="D7" t="n">
-        <v>0.16177213170115</v>
+        <v>0.1656526542779681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08088606585057501</v>
+        <v>0.08282632713898405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06916545598832109</v>
+        <v>0.07082456816466567</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39250</v>
+        <v>40250</v>
       </c>
       <c r="C8" t="n">
-        <v>29512.91247619047</v>
+        <v>29754.91247619047</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1696848401041912</v>
+        <v>0.1735113489669453</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08484242005209558</v>
+        <v>0.08675567448347266</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07068021062076105</v>
+        <v>0.07227409757139024</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38750</v>
+        <v>39225</v>
       </c>
       <c r="C9" t="n">
-        <v>30280.80733333333</v>
+        <v>30429.95733333333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1832245395496566</v>
+        <v>0.1855868837510448</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09161226977482828</v>
+        <v>0.09279344187552242</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0743545733096569</v>
+        <v>0.07531323908410227</v>
       </c>
     </row>
     <row r="10">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37700</v>
+        <v>38225</v>
       </c>
       <c r="C10" t="n">
-        <v>30369.05052380952</v>
+        <v>30553.32552380952</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1920605017183326</v>
+        <v>0.1940897798244999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09603025085916631</v>
+        <v>0.09704488991224994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07593314032030331</v>
+        <v>0.07673543677275399</v>
       </c>
     </row>
     <row r="11">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6916818419109154</v>
+        <v>0.6998678069084122</v>
       </c>
     </row>
     <row r="13">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.329223524809156</v>
+        <v>2.348949352633733</v>
       </c>
       <c r="F13" t="n">
-        <v>1.748126981966651</v>
+        <v>1.762931594531517</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.439808823877566</v>
+        <v>2.462799401439929</v>
       </c>
     </row>
     <row r="15">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42481.25</v>
+        <v>44825</v>
       </c>
     </row>
   </sheetData>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.480633534631111</v>
+        <v>1.496402223925856</v>
       </c>
       <c r="C2" t="n">
-        <v>1.783037143015192</v>
+        <v>1.800280880424487</v>
       </c>
       <c r="D2" t="n">
-        <v>2.085440751399275</v>
+        <v>2.104159536923119</v>
       </c>
       <c r="E2" t="n">
-        <v>2.387844359783355</v>
+        <v>2.408038193421749</v>
       </c>
       <c r="F2" t="n">
-        <v>2.690247968167437</v>
+        <v>2.71191684992038</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.502565917026686</v>
+        <v>1.519184957259648</v>
       </c>
       <c r="C3" t="n">
-        <v>1.804969525410768</v>
+        <v>1.823063613758279</v>
       </c>
       <c r="D3" t="n">
-        <v>2.10737313379485</v>
+        <v>2.12694227025691</v>
       </c>
       <c r="E3" t="n">
-        <v>2.409776742178931</v>
+        <v>2.430820926755541</v>
       </c>
       <c r="F3" t="n">
-        <v>2.712180350563012</v>
+        <v>2.734699583254172</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.524498299422262</v>
+        <v>1.54196769059344</v>
       </c>
       <c r="C4" t="n">
-        <v>1.826901907806343</v>
+        <v>1.845846347092071</v>
       </c>
       <c r="D4" t="n">
-        <v>2.129305516190425</v>
+        <v>2.149725003590702</v>
       </c>
       <c r="E4" t="n">
-        <v>2.431709124574506</v>
+        <v>2.453603660089334</v>
       </c>
       <c r="F4" t="n">
-        <v>2.734112732958587</v>
+        <v>2.757482316587964</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.546430681817837</v>
+        <v>1.564750423927232</v>
       </c>
       <c r="C5" t="n">
-        <v>1.848834290201918</v>
+        <v>1.868629080425863</v>
       </c>
       <c r="D5" t="n">
-        <v>2.151237898586</v>
+        <v>2.172507736924494</v>
       </c>
       <c r="E5" t="n">
-        <v>2.453641506970081</v>
+        <v>2.476386393423125</v>
       </c>
       <c r="F5" t="n">
-        <v>2.756045115354162</v>
+        <v>2.780265049921756</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.568363064213412</v>
+        <v>1.587533157261024</v>
       </c>
       <c r="C6" t="n">
-        <v>1.870766672597493</v>
+        <v>1.891411813759655</v>
       </c>
       <c r="D6" t="n">
-        <v>2.173170280981575</v>
+        <v>2.195290470258286</v>
       </c>
       <c r="E6" t="n">
-        <v>2.475573889365656</v>
+        <v>2.499169126756917</v>
       </c>
       <c r="F6" t="n">
-        <v>2.777977497749737</v>
+        <v>2.803047783255549</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="3">
@@ -1279,7 +1279,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>132543.4122991888</v>
+        <v>124928.307269277</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.437865933277382</v>
+        <v>3.240347929881121</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>124928.307269277</v>
+        <v>112236.4655527574</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.240347929881121</v>
+        <v>2.911151257554024</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112236.4655527574</v>
+        <v>130005.0439558848</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.911151257554024</v>
+        <v>3.372026598811958</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.51</v>
+        <v>2.5376</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>130005.0439558848</v>
+        <v>137010.9405834037</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.372026598811958</v>
+        <v>3.553743161936519</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5376</v>
+        <v>2.4844</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137010.9405834037</v>
+        <v>123506.8209970268</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.553743161936519</v>
+        <v>3.203477902580486</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.4844</v>
+        <v>2.4627</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.209783772116895</v>
+        <v>2.210425998652053</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.462799401439929</v>
+        <v>2.464404967777827</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.310820323135168</v>
+        <v>1.317371709574792</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>123506.8209970268</v>
+        <v>117817.5944213071</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.203477902580486</v>
+        <v>3.047395909396207</v>
       </c>
     </row>
   </sheetData>
@@ -866,13 +866,13 @@
         <v>27013.544</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1352631264630104</v>
+        <v>0.1353135123903089</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0676315632315052</v>
+        <v>0.06765675619515443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06253990132855246</v>
+        <v>0.06256319763260806</v>
       </c>
     </row>
     <row r="5">
@@ -888,13 +888,13 @@
         <v>28735.85323809524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1459371771488864</v>
+        <v>0.1460883349307818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0729685885744432</v>
+        <v>0.07304416746539089</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06573746718418307</v>
+        <v>0.06580555627512692</v>
       </c>
     </row>
     <row r="6">
@@ -910,13 +910,13 @@
         <v>29054.65533333334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1548850100820818</v>
+        <v>0.1551368389467195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07744250504104089</v>
+        <v>0.07756841947335975</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06797131455830406</v>
+        <v>0.0680818297008868</v>
       </c>
     </row>
     <row r="7">
@@ -932,13 +932,13 @@
         <v>29765.03028571429</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1656526542779681</v>
+        <v>0.1660051542253482</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08282632713898405</v>
+        <v>0.08300257711267409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07082456816466567</v>
+        <v>0.07097527904014231</v>
       </c>
     </row>
     <row r="8">
@@ -954,13 +954,13 @@
         <v>29754.91247619047</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1735113489669453</v>
+        <v>0.1740655941672284</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08675567448347266</v>
+        <v>0.08703279708361418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07227409757139024</v>
+        <v>0.07250496184581509</v>
       </c>
     </row>
     <row r="9">
@@ -976,13 +976,13 @@
         <v>30429.95733333333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1855868837510448</v>
+        <v>0.1862420015777794</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09279344187552242</v>
+        <v>0.09312100078888971</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07531323908410227</v>
+        <v>0.07557909324640021</v>
       </c>
     </row>
     <row r="10">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6998678069084122</v>
+        <v>0.7007171367581939</v>
       </c>
     </row>
     <row r="13">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.348949352633733</v>
+        <v>2.349956970407847</v>
       </c>
       <c r="F13" t="n">
-        <v>1.762931594531517</v>
+        <v>1.763687831019633</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.462799401439929</v>
+        <v>2.464404967777827</v>
       </c>
     </row>
     <row r="15">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.496402223925856</v>
+        <v>1.496863124766028</v>
       </c>
       <c r="C2" t="n">
-        <v>1.800280880424487</v>
+        <v>1.800741781264659</v>
       </c>
       <c r="D2" t="n">
-        <v>2.104159536923119</v>
+        <v>2.104620437763291</v>
       </c>
       <c r="E2" t="n">
-        <v>2.408038193421749</v>
+        <v>2.408499094261922</v>
       </c>
       <c r="F2" t="n">
-        <v>2.71191684992038</v>
+        <v>2.712377750760553</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.519184957259648</v>
+        <v>1.519744622565572</v>
       </c>
       <c r="C3" t="n">
-        <v>1.823063613758279</v>
+        <v>1.823623279064202</v>
       </c>
       <c r="D3" t="n">
-        <v>2.12694227025691</v>
+        <v>2.127501935562834</v>
       </c>
       <c r="E3" t="n">
-        <v>2.430820926755541</v>
+        <v>2.431380592061466</v>
       </c>
       <c r="F3" t="n">
-        <v>2.734699583254172</v>
+        <v>2.735259248560096</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.54196769059344</v>
+        <v>1.542626120365115</v>
       </c>
       <c r="C4" t="n">
-        <v>1.845846347092071</v>
+        <v>1.846504776863746</v>
       </c>
       <c r="D4" t="n">
-        <v>2.149725003590702</v>
+        <v>2.150383433362378</v>
       </c>
       <c r="E4" t="n">
-        <v>2.453603660089334</v>
+        <v>2.454262089861008</v>
       </c>
       <c r="F4" t="n">
-        <v>2.757482316587964</v>
+        <v>2.75814074635964</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.564750423927232</v>
+        <v>1.565507618164658</v>
       </c>
       <c r="C5" t="n">
-        <v>1.868629080425863</v>
+        <v>1.869386274663289</v>
       </c>
       <c r="D5" t="n">
-        <v>2.172507736924494</v>
+        <v>2.173264931161921</v>
       </c>
       <c r="E5" t="n">
-        <v>2.476386393423125</v>
+        <v>2.477143587660552</v>
       </c>
       <c r="F5" t="n">
-        <v>2.780265049921756</v>
+        <v>2.781022244159183</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.587533157261024</v>
+        <v>1.588389115964202</v>
       </c>
       <c r="C6" t="n">
-        <v>1.891411813759655</v>
+        <v>1.892267772462833</v>
       </c>
       <c r="D6" t="n">
-        <v>2.195290470258286</v>
+        <v>2.196146428961464</v>
       </c>
       <c r="E6" t="n">
-        <v>2.499169126756917</v>
+        <v>2.500025085460095</v>
       </c>
       <c r="F6" t="n">
-        <v>2.803047783255549</v>
+        <v>2.803903741958726</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.4627</v>
+        <v>2.5974</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>117817.5944213071</v>
+        <v>151956.9780729332</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.047395909396207</v>
+        <v>3.930423767843626</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5974</v>
+        <v>2.5699</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>151956.9780729332</v>
+        <v>144987.1707201514</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.930423767843626</v>
+        <v>3.75014710780425</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5699</v>
+        <v>2.5565</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>144987.1707201514</v>
+        <v>141590.9736827959</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.75014710780425</v>
+        <v>3.662303208003246</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.210425998652053</v>
+        <v>2.217504814969312</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.041106685901538</v>
+        <v>2.050371573772689</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.464404967777827</v>
+        <v>2.468204676764246</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.317371709574792</v>
+        <v>1.316986823514281</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>141590.9736827959</v>
+        <v>139574.0984435705</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.662303208003246</v>
+        <v>3.613954708459896</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>440.8073816635988</v>
+        <v>444.9182149969322</v>
       </c>
     </row>
     <row r="3">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>905.639606003278</v>
+        <v>909.7504393366113</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.041106685901538</v>
+        <v>2.050371573772689</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.041106685901538</v>
+        <v>2.050371573772689</v>
       </c>
     </row>
     <row r="14">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.349956970407847</v>
+        <v>2.355019744250878</v>
       </c>
       <c r="F13" t="n">
-        <v>1.763687831019633</v>
+        <v>1.767487540006052</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.464404967777827</v>
+        <v>2.468204676764246</v>
       </c>
     </row>
     <row r="15">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.496863124766028</v>
+        <v>1.502763317224228</v>
       </c>
       <c r="C2" t="n">
-        <v>1.800741781264659</v>
+        <v>1.807379497780134</v>
       </c>
       <c r="D2" t="n">
-        <v>2.104620437763291</v>
+        <v>2.111995678336041</v>
       </c>
       <c r="E2" t="n">
-        <v>2.408499094261922</v>
+        <v>2.416611858891947</v>
       </c>
       <c r="F2" t="n">
-        <v>2.712377750760553</v>
+        <v>2.721228039447852</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.519744622565572</v>
+        <v>1.525644815023771</v>
       </c>
       <c r="C3" t="n">
-        <v>1.823623279064202</v>
+        <v>1.830260995579677</v>
       </c>
       <c r="D3" t="n">
-        <v>2.127501935562834</v>
+        <v>2.134877176135584</v>
       </c>
       <c r="E3" t="n">
-        <v>2.431380592061466</v>
+        <v>2.43949335669149</v>
       </c>
       <c r="F3" t="n">
-        <v>2.735259248560096</v>
+        <v>2.744109537247396</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.542626120365115</v>
+        <v>1.548526312823315</v>
       </c>
       <c r="C4" t="n">
-        <v>1.846504776863746</v>
+        <v>1.85314249337922</v>
       </c>
       <c r="D4" t="n">
-        <v>2.150383433362378</v>
+        <v>2.157758673935127</v>
       </c>
       <c r="E4" t="n">
-        <v>2.454262089861008</v>
+        <v>2.462374854491033</v>
       </c>
       <c r="F4" t="n">
-        <v>2.75814074635964</v>
+        <v>2.766991035046939</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.565507618164658</v>
+        <v>1.571407810622858</v>
       </c>
       <c r="C5" t="n">
-        <v>1.869386274663289</v>
+        <v>1.876023991178764</v>
       </c>
       <c r="D5" t="n">
-        <v>2.173264931161921</v>
+        <v>2.18064017173467</v>
       </c>
       <c r="E5" t="n">
-        <v>2.477143587660552</v>
+        <v>2.485256352290576</v>
       </c>
       <c r="F5" t="n">
-        <v>2.781022244159183</v>
+        <v>2.789872532846482</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.588389115964202</v>
+        <v>1.594289308422401</v>
       </c>
       <c r="C6" t="n">
-        <v>1.892267772462833</v>
+        <v>1.898905488978307</v>
       </c>
       <c r="D6" t="n">
-        <v>2.196146428961464</v>
+        <v>2.203521669534214</v>
       </c>
       <c r="E6" t="n">
-        <v>2.500025085460095</v>
+        <v>2.50813785009012</v>
       </c>
       <c r="F6" t="n">
-        <v>2.803903741958726</v>
+        <v>2.812754030646026</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="3">
@@ -1279,7 +1279,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5565</v>
+        <v>2.5462</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>139574.0984435705</v>
+        <v>136966.3472070439</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.613954708459896</v>
+        <v>3.546432904881506</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5462</v>
+        <v>2.7173</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>136966.3472070439</v>
+        <v>180285.3993011871</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.546432904881506</v>
+        <v>4.668081506071951</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.7173</v>
+        <v>3.0146</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180285.3993011871</v>
+        <v>255555.733536072</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.668081506071951</v>
+        <v>6.617036088970373</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0146</v>
+        <v>2.8535</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255555.733536072</v>
+        <v>214768.4787589447</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.617036088970373</v>
+        <v>5.560942636885153</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.8535</v>
+        <v>2.8536</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214768.4787589447</v>
+        <v>214793.7967321149</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.560942636885153</v>
+        <v>5.561598188376207</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mpcc_fv_report.xlsx
+++ b/outputs/mpcc_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.217504814969312</v>
+        <v>2.28704218604123</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.050371573772689</v>
+        <v>2.103866834481654</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.468204676764246</v>
+        <v>2.561805213380592</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.316986823514281</v>
+        <v>1.319082060274878</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214793.7967321149</v>
+        <v>192189.7028085543</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.561598188376207</v>
+        <v>4.94526154191108</v>
       </c>
     </row>
   </sheetData>
@@ -629,21 +629,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fleet value — Ctr-Feeder</t>
+          <t>Fleet value — Ctr-Intermediate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>444.9182149969322</v>
+        <v>1060.73790430916</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fleet value — Ctr-Intermediate</t>
+          <t>Fleet value — Ctr-Feeder</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1093.332224339679</v>
+        <v>408.285397129196</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>269.3</v>
+        <v>314.052</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85.90000000000001</v>
+        <v>100.763</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-462.9</v>
+        <v>-436.789</v>
       </c>
     </row>
     <row r="7">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-633.7</v>
+        <v>-631.7</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112.9</v>
+        <v>118.137</v>
       </c>
     </row>
     <row r="10">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>909.7504393366113</v>
+        <v>933.4863014383569</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.050371573772689</v>
+        <v>2.103866834481654</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.050371573772689</v>
+        <v>2.103866834481654</v>
       </c>
     </row>
     <row r="14">
@@ -774,7 +774,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -819,16 +819,16 @@
         <v>46350</v>
       </c>
       <c r="C2" t="n">
-        <v>26404.2380952381</v>
+        <v>26531.70731707317</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1285357879267489</v>
+        <v>0.1295393827375522</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06426789396337446</v>
+        <v>0.06476969136877608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06261282857571353</v>
+        <v>0.06310170339308432</v>
       </c>
     </row>
     <row r="3">
@@ -841,16 +841,16 @@
         <v>45325</v>
       </c>
       <c r="C3" t="n">
-        <v>26404.2380952381</v>
+        <v>26531.70731707317</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1312469405351294</v>
+        <v>0.1268146213482623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0656234702675647</v>
+        <v>0.06340731067413113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06228704151348542</v>
+        <v>0.06018355591551434</v>
       </c>
     </row>
     <row r="4">
@@ -863,16 +863,16 @@
         <v>44325</v>
       </c>
       <c r="C4" t="n">
-        <v>27013.544</v>
+        <v>27136.67926829269</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1353135123903089</v>
+        <v>0.1373252701333067</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06765675619515443</v>
+        <v>0.06866263506665336</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06256319763260806</v>
+        <v>0.06349334862078919</v>
       </c>
     </row>
     <row r="5">
@@ -885,16 +885,16 @@
         <v>43300</v>
       </c>
       <c r="C5" t="n">
-        <v>28735.85323809524</v>
+        <v>28845.73170731707</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1460883349307818</v>
+        <v>0.1552164775685208</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07304416746539089</v>
+        <v>0.07760823878426039</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06580555627512692</v>
+        <v>0.06991733223807242</v>
       </c>
     </row>
     <row r="6">
@@ -907,16 +907,16 @@
         <v>42275</v>
       </c>
       <c r="C6" t="n">
-        <v>29054.65533333334</v>
+        <v>29160.83719512195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1551368389467195</v>
+        <v>0.1657751853398157</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07756841947335975</v>
+        <v>0.08288759266990785</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0680818297008868</v>
+        <v>0.07275046993070718</v>
       </c>
     </row>
     <row r="7">
@@ -929,16 +929,16 @@
         <v>41275</v>
       </c>
       <c r="C7" t="n">
-        <v>29765.03028571429</v>
+        <v>29863.69146341464</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1660051542253482</v>
+        <v>0.1786176398822028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08300257711267409</v>
+        <v>0.08930881994110138</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07097527904014231</v>
+        <v>0.07636773021469963</v>
       </c>
     </row>
     <row r="8">
@@ -951,16 +951,16 @@
         <v>40250</v>
       </c>
       <c r="C8" t="n">
-        <v>29754.91247619047</v>
+        <v>29851.53414634146</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1740655941672284</v>
+        <v>0.1866901659187762</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08703279708361418</v>
+        <v>0.09334508295938808</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07250496184581509</v>
+        <v>0.07776357770005644</v>
       </c>
     </row>
     <row r="9">
@@ -973,16 +973,16 @@
         <v>39225</v>
       </c>
       <c r="C9" t="n">
-        <v>30429.95733333333</v>
+        <v>30517.40121951219</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1862420015777794</v>
+        <v>0.1994624934012847</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09312100078888971</v>
+        <v>0.09973124670064237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07557909324640021</v>
+        <v>0.08094411711763846</v>
       </c>
     </row>
     <row r="10">
@@ -995,16 +995,16 @@
         <v>38225</v>
       </c>
       <c r="C10" t="n">
-        <v>30553.32552380952</v>
+        <v>30636.05304878049</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1940897798244999</v>
+        <v>0.1986084360804426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09704488991224994</v>
+        <v>0.09930421804022131</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07673543677275399</v>
+        <v>0.07852193507132095</v>
       </c>
     </row>
     <row r="11">
@@ -1017,16 +1017,16 @@
         <v>37200</v>
       </c>
       <c r="C11" t="n">
-        <v>32493.04780952381</v>
+        <v>32548.62439024391</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2169690471497597</v>
+        <v>0.2124505149271054</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1084845235748798</v>
+        <v>0.1062252574635527</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08357191215526147</v>
+        <v>0.08183146860839124</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7007171367581939</v>
+        <v>0.7248752388102742</v>
       </c>
     </row>
     <row r="13">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.355019744250878</v>
+        <v>2.447545604143014</v>
       </c>
       <c r="F13" t="n">
-        <v>1.767487540006052</v>
+        <v>1.836929974570318</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.468204676764246</v>
+        <v>2.561805213380592</v>
       </c>
     </row>
     <row r="15">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.502763317224228</v>
+        <v>1.598260356955739</v>
       </c>
       <c r="C2" t="n">
-        <v>1.807379497780134</v>
+        <v>1.888724738977997</v>
       </c>
       <c r="D2" t="n">
-        <v>2.111995678336041</v>
+        <v>2.179189121000257</v>
       </c>
       <c r="E2" t="n">
-        <v>2.416611858891947</v>
+        <v>2.469653503022515</v>
       </c>
       <c r="F2" t="n">
-        <v>2.721228039447852</v>
+        <v>2.760117885044775</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.525644815023771</v>
+        <v>1.62208966189991</v>
       </c>
       <c r="C3" t="n">
-        <v>1.830260995579677</v>
+        <v>1.912554043922169</v>
       </c>
       <c r="D3" t="n">
-        <v>2.134877176135584</v>
+        <v>2.203018425944429</v>
       </c>
       <c r="E3" t="n">
-        <v>2.43949335669149</v>
+        <v>2.493482807966686</v>
       </c>
       <c r="F3" t="n">
-        <v>2.744109537247396</v>
+        <v>2.783947189988946</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.548526312823315</v>
+        <v>1.645918966844081</v>
       </c>
       <c r="C4" t="n">
-        <v>1.85314249337922</v>
+        <v>1.93638334886634</v>
       </c>
       <c r="D4" t="n">
-        <v>2.157758673935127</v>
+        <v>2.2268477308886</v>
       </c>
       <c r="E4" t="n">
-        <v>2.462374854491033</v>
+        <v>2.517312112910858</v>
       </c>
       <c r="F4" t="n">
-        <v>2.766991035046939</v>
+        <v>2.807776494933117</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.571407810622858</v>
+        <v>1.669748271788252</v>
       </c>
       <c r="C5" t="n">
-        <v>1.876023991178764</v>
+        <v>1.960212653810511</v>
       </c>
       <c r="D5" t="n">
-        <v>2.18064017173467</v>
+        <v>2.250677035832771</v>
       </c>
       <c r="E5" t="n">
-        <v>2.485256352290576</v>
+        <v>2.541141417855028</v>
       </c>
       <c r="F5" t="n">
-        <v>2.789872532846482</v>
+        <v>2.831605799877288</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.594289308422401</v>
+        <v>1.693577576732423</v>
       </c>
       <c r="C6" t="n">
-        <v>1.898905488978307</v>
+        <v>1.984041958754682</v>
       </c>
       <c r="D6" t="n">
-        <v>2.203521669534214</v>
+        <v>2.274506340776942</v>
       </c>
       <c r="E6" t="n">
-        <v>2.50813785009012</v>
+        <v>2.5649707227992</v>
       </c>
       <c r="F6" t="n">
-        <v>2.812754030646026</v>
+        <v>2.855435104821459</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="3">
@@ -1279,7 +1279,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>
